--- a/artfynd/A 3721-2023 artfynd.xlsx
+++ b/artfynd/A 3721-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3721-2023 artfynd.xlsx
+++ b/artfynd/A 3721-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1009,6 +1009,130 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124011130</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57861</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bommen, B-plan Borensberg, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>516958</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6491947</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Brunneby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Peter Berry</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Peter Berry</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3721-2023 artfynd.xlsx
+++ b/artfynd/A 3721-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89120425</v>
+        <v>89120490</v>
       </c>
       <c r="B2" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517099.0394730351</v>
+        <v>517113</v>
       </c>
       <c r="R2" t="n">
-        <v>6491920.22153538</v>
+        <v>6491910</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2020-11-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-11-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89120490</v>
+        <v>89120425</v>
       </c>
       <c r="B3" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>2590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517113.1942570256</v>
+        <v>517099</v>
       </c>
       <c r="R3" t="n">
-        <v>6491909.851259033</v>
+        <v>6491920</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2020-11-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-11-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89120427</v>
+        <v>89120426</v>
       </c>
       <c r="B4" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517108.1308571227</v>
+        <v>517127</v>
       </c>
       <c r="R4" t="n">
-        <v>6491872.794317444</v>
+        <v>6491902</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2020-11-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-11-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124011130</v>
+        <v>89120427</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,49 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>2590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bommen, B-plan Borensberg, Ög</t>
+          <t>Salsjöskogen, Borensberg, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516958</v>
+        <v>517108</v>
       </c>
       <c r="R5" t="n">
-        <v>6491947</v>
+        <v>6491873</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>19:26</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>19:26</t>
+          <t>2020-11-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1051,358 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124011130</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bommen, B-plan Borensberg, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>516958</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6491947</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Brunneby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Peter Berry</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Peter Berry</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>55977703</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Borensberg, 250 m SSV Salsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>517067</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6491617</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Brunneby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2015-08-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2015-08-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>30-tal stänglar inom cirka 20x20 meter. Bladskivor därutöver inom området.. Gammal barrskog.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Göran Börkén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Göran Börkén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121152535</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Borensberg, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>517070</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6491610</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Brunneby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3721-2023 artfynd.xlsx
+++ b/artfynd/A 3721-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1088,27 +1088,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124011130</v>
+        <v>136184749</v>
       </c>
       <c r="B6" t="n">
-        <v>58327</v>
+        <v>57995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1118,30 +1118,30 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bommen, B-plan Borensberg, Ög</t>
+          <t>Salsjön, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516958</v>
+        <v>516848</v>
       </c>
       <c r="R6" t="n">
-        <v>6491947</v>
+        <v>6491995</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>06:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>06:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,76 +1195,77 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peter Berry</t>
+          <t>Martin Berry</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Berry</t>
+          <t>Martin Berry</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124011130</t>
+          <t>https://artportalen.se/Sighting/136184749</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>55977703</v>
+        <v>124011130</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Borensberg, 250 m SSV Salsjön, Ög</t>
+          <t>Bommen, B-plan Borensberg, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517067</v>
+        <v>516958</v>
       </c>
       <c r="R7" t="n">
-        <v>6491617</v>
+        <v>6491947</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,17 +1289,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-08-05</t>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-08-05</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>30-tal stänglar inom cirka 20x20 meter. Bladskivor därutöver inom området.. Gammal barrskog.</t>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,33 +1315,28 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Börkén</t>
+          <t>Peter Berry</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Börkén</t>
+          <t>Peter Berry</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55977703</t>
+          <t>https://artportalen.se/Sighting/124011130</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121152535</v>
+        <v>55977703</v>
       </c>
       <c r="B8" t="n">
         <v>99118</v>
@@ -1365,22 +1366,29 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Borensberg, Ög</t>
+          <t>Borensberg, 250 m SSV Salsjön, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517070</v>
+        <v>517067</v>
       </c>
       <c r="R8" t="n">
-        <v>6491610</v>
+        <v>6491617</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,17 +1412,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2015-08-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2015-08-05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>30-tal stänglar inom cirka 20x20 meter. Bladskivor därutöver inom området.. Gammal barrskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,20 +1433,136 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Göran Börkén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Göran Börkén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55977703</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121152535</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Borensberg, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>517070</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6491610</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Brunneby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/121152535</t>
         </is>
@@ -1453,6 +1577,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3721-2023 artfynd.xlsx
+++ b/artfynd/A 3721-2023 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>136184749</v>
       </c>
       <c r="B6" t="n">
-        <v>57995</v>
+        <v>57996</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3721-2023 artfynd.xlsx
+++ b/artfynd/A 3721-2023 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>136184749</v>
       </c>
       <c r="B6" t="n">
-        <v>57996</v>
+        <v>58000</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3721-2023 artfynd.xlsx
+++ b/artfynd/A 3721-2023 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>136184749</v>
       </c>
       <c r="B6" t="n">
-        <v>58000</v>
+        <v>58001</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3721-2023 artfynd.xlsx
+++ b/artfynd/A 3721-2023 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>136184749</v>
       </c>
       <c r="B6" t="n">
-        <v>58001</v>
+        <v>58006</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3721-2023 artfynd.xlsx
+++ b/artfynd/A 3721-2023 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>136184749</v>
       </c>
       <c r="B6" t="n">
-        <v>58006</v>
+        <v>58019</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
